--- a/config/配置编辑器.xlsx
+++ b/config/配置编辑器.xlsx
@@ -79489,7 +79489,9 @@
           <t>收入</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr"/>
+      <c r="C4" s="10" t="n">
+        <v>7179.465664</v>
+      </c>
       <c r="D4" s="11" t="inlineStr">
         <is>
           <t>月度达成页的 KPI 指标总数</t>
